--- a/downloads/pages.xlsx
+++ b/downloads/pages.xlsx
@@ -463,7 +463,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Every web page, by site menu</t>
+          <t>Johnson, Levy and NutraGen websites: every page</t>
         </is>
       </c>
     </row>

--- a/downloads/pages.xlsx
+++ b/downloads/pages.xlsx
@@ -463,7 +463,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Johnson, Levy and NutraGen websites: every page</t>
+          <t>Archived pages from Dr. Johnson's, Dr. Levy's and NutraGen's websites</t>
         </is>
       </c>
     </row>

--- a/downloads/pages.xlsx
+++ b/downloads/pages.xlsx
@@ -8,16 +8,16 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Index" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="movepastyourpain.com Dr. Johnso" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="johnsonchiropracticgroup.wordpr" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="formagym.com Dr. Johnson (Trusa" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="trusalus.com Dr. Johnson, 123 p" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="truchiropractors.com Dr. Johnso" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="neuromuscularreeducation.com Dr" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="nmrseminars.com Dr. Levy, 35 pa" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="drpeterlevy.com Dr. Levy, 10 pa" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="28daystohealth.com Dr. Johnson," sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="nutragen.com Dr. Johnson (Nutra" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="movepastyourpain.com" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Johnson WordPress blog" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="formagym.com" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="trusalus.com" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="truchiropractors.com" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="neuromuscularreeducation.com" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="nmrseminars.com" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="drpeterlevy.com" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="28daystohealth.com" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="nutragen.com" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -494,7 +494,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>movepastyourpain.com Dr. Johnso</t>
+          <t>movepastyourpain.com</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -509,7 +509,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>johnsonchiropracticgroup.wordpr</t>
+          <t>Johnson WordPress blog</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -524,7 +524,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>formagym.com Dr. Johnson (Trusa</t>
+          <t>formagym.com</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -539,7 +539,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>trusalus.com Dr. Johnson, 123 p</t>
+          <t>trusalus.com</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -554,7 +554,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>truchiropractors.com Dr. Johnso</t>
+          <t>truchiropractors.com</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -569,7 +569,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>neuromuscularreeducation.com Dr</t>
+          <t>neuromuscularreeducation.com</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -584,7 +584,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>nmrseminars.com Dr. Levy, 35 pa</t>
+          <t>nmrseminars.com</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -599,7 +599,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>drpeterlevy.com Dr. Levy, 10 pa</t>
+          <t>drpeterlevy.com</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -614,7 +614,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>28daystohealth.com Dr. Johnson,</t>
+          <t>28daystohealth.com</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -629,7 +629,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>nutragen.com Dr. Johnson (Nutra</t>
+          <t>nutragen.com</t>
         </is>
       </c>
       <c r="B14" t="n">

--- a/downloads/pages.xlsx
+++ b/downloads/pages.xlsx
@@ -671,7 +671,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -731,7 +731,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -765,7 +765,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -819,7 +819,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -873,7 +873,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1333,7 +1333,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1725,7 +1725,7 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1816,7 +1816,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1984,7 +1984,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2180,7 +2180,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2207,7 +2207,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2322,7 +2322,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2437,7 +2437,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2464,7 +2464,7 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2518,7 +2518,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2721,7 +2721,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2803,7 +2803,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2897,7 +2897,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2978,7 +2978,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3113,7 +3113,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3147,7 +3147,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3228,7 +3228,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3309,7 +3309,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3424,7 +3424,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3532,7 +3532,7 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3586,7 +3586,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3613,7 +3613,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3721,7 +3721,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3802,7 +3802,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3897,7 +3897,7 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4113,7 +4113,7 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4208,7 +4208,7 @@
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4262,7 +4262,7 @@
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4323,7 +4323,7 @@
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4384,7 +4384,7 @@
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4418,7 +4418,7 @@
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4452,7 +4452,7 @@
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4479,7 +4479,7 @@
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4506,7 +4506,7 @@
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4533,7 +4533,7 @@
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4560,7 +4560,7 @@
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4614,7 +4614,7 @@
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4641,7 +4641,7 @@
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4722,7 +4722,7 @@
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4927,7 +4927,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5012,7 +5012,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5099,7 +5099,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5194,7 +5194,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5227,7 +5227,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5321,7 +5321,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5355,7 +5355,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5436,7 +5436,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5463,7 +5463,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5517,7 +5517,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5571,7 +5571,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5679,7 +5679,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5706,7 +5706,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5733,7 +5733,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5767,7 +5767,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5855,7 +5855,7 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5882,7 +5882,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5909,7 +5909,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5943,7 +5943,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5970,7 +5970,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6038,7 +6038,7 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6077,7 +6077,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6104,7 +6104,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6185,7 +6185,7 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6212,7 +6212,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6251,7 +6251,7 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6312,7 +6312,7 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6339,7 +6339,7 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6447,7 +6447,7 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6508,7 +6508,7 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6617,7 +6617,7 @@
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6651,7 @@
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6678,7 +6678,7 @@
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6712,7 +6712,7 @@
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6739,7 +6739,7 @@
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6766,7 +6766,7 @@
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6793,7 +6793,7 @@
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6827,7 +6827,7 @@
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6854,7 +6854,7 @@
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6881,7 +6881,7 @@
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6908,7 +6908,7 @@
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6935,7 +6935,7 @@
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6962,7 +6962,7 @@
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6989,7 +6989,7 @@
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7016,7 +7016,7 @@
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7070,7 +7070,7 @@
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7104,7 +7104,7 @@
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7131,7 +7131,7 @@
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7158,7 +7158,7 @@
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7185,7 +7185,7 @@
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7239,7 +7239,7 @@
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7300,7 +7300,7 @@
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7368,7 +7368,7 @@
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7395,7 +7395,7 @@
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7449,7 +7449,7 @@
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7476,7 +7476,7 @@
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7537,7 +7537,7 @@
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7564,7 +7564,7 @@
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7591,7 +7591,7 @@
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7645,7 +7645,7 @@
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7733,7 +7733,7 @@
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7760,7 +7760,7 @@
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7787,7 +7787,7 @@
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7841,7 +7841,7 @@
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7868,7 +7868,7 @@
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7895,7 +7895,7 @@
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7948,7 +7948,7 @@
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7975,7 +7975,7 @@
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8002,7 +8002,7 @@
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8029,7 +8029,7 @@
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8056,7 +8056,7 @@
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8083,7 +8083,7 @@
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8110,7 +8110,7 @@
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8137,7 +8137,7 @@
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8164,7 +8164,7 @@
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8191,7 +8191,7 @@
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8218,7 +8218,7 @@
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8252,7 +8252,7 @@
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8279,7 +8279,7 @@
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8306,7 +8306,7 @@
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8333,7 +8333,7 @@
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8387,7 +8387,7 @@
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8414,7 +8414,7 @@
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8468,7 +8468,7 @@
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8495,7 +8495,7 @@
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8522,7 +8522,7 @@
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8549,7 +8549,7 @@
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8576,7 +8576,7 @@
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8603,7 +8603,7 @@
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8657,7 +8657,7 @@
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8684,7 +8684,7 @@
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8711,7 +8711,7 @@
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8745,7 +8745,7 @@
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8772,7 +8772,7 @@
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8799,7 +8799,7 @@
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8826,7 +8826,7 @@
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9055,7 +9055,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9115,7 +9115,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9142,7 +9142,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9169,7 +9169,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9196,7 +9196,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9223,7 +9223,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9257,7 +9257,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9284,7 +9284,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9311,7 +9311,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9338,7 +9338,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9365,7 +9365,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9392,7 +9392,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9419,7 +9419,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9480,7 +9480,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9507,7 +9507,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9561,7 +9561,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9588,7 +9588,7 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9615,7 +9615,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9675,7 +9675,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9735,7 +9735,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9769,7 +9769,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9796,7 +9796,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9830,7 +9830,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9857,7 +9857,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9884,7 +9884,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9918,7 +9918,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9952,7 +9952,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9979,7 +9979,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10013,7 +10013,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10047,7 +10047,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10090,7 +10090,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10150,7 +10150,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10184,7 +10184,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10211,7 +10211,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10238,7 +10238,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10265,7 +10265,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10299,7 +10299,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10326,7 +10326,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10353,7 +10353,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10380,7 +10380,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10407,7 +10407,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10495,7 +10495,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10529,7 +10529,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10556,7 +10556,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10590,7 +10590,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10624,7 +10624,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10658,7 +10658,7 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10692,7 +10692,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10726,7 +10726,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10760,7 +10760,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10794,7 +10794,7 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10821,7 +10821,7 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10848,7 +10848,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10875,7 +10875,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10902,7 +10902,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10929,7 +10929,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10956,7 +10956,7 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10983,7 +10983,7 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -11010,7 +11010,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -11037,7 +11037,7 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -11064,7 +11064,7 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -11091,7 +11091,7 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -11125,7 +11125,7 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -11152,7 +11152,7 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -11233,7 +11233,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11293,7 +11293,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -11320,7 +11320,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -11347,7 +11347,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -11401,7 +11401,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -11428,7 +11428,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -11462,7 +11462,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -11489,7 +11489,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -11516,7 +11516,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -11543,7 +11543,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>last copy · first copy · all dates</t>
+          <t>last copy · first copy · latest saved copy</t>
         </is>
       </c>
     </row>
